--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/10.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/10.xlsx
@@ -426,13 +426,13 @@
         <v>-15.05160926105479</v>
       </c>
       <c r="E2">
-        <v>-27.24241412594697</v>
+        <v>-23.99432991615334</v>
       </c>
       <c r="F2">
-        <v>-3.104794897638904</v>
+        <v>-1.818413217422718</v>
       </c>
       <c r="G2">
-        <v>-16.6286264140576</v>
+        <v>-14.57410019711313</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.75043781939544</v>
       </c>
       <c r="E3">
-        <v>-27.47925784502214</v>
+        <v>-24.05637001005843</v>
       </c>
       <c r="F3">
-        <v>-2.879178266710222</v>
+        <v>-1.804184350544831</v>
       </c>
       <c r="G3">
-        <v>-16.16017925443242</v>
+        <v>-14.39916600499973</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.33678770544992</v>
       </c>
       <c r="E4">
-        <v>-27.99988744473598</v>
+        <v>-23.98516881323583</v>
       </c>
       <c r="F4">
-        <v>-2.884432601146179</v>
+        <v>-1.831624020762565</v>
       </c>
       <c r="G4">
-        <v>-16.16341365742429</v>
+        <v>-13.73385228906348</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.81889975812506</v>
       </c>
       <c r="E5">
-        <v>-27.89759374537672</v>
+        <v>-24.9963046035645</v>
       </c>
       <c r="F5">
-        <v>-2.904448442700024</v>
+        <v>-1.78104473551503</v>
       </c>
       <c r="G5">
-        <v>-16.10199145076142</v>
+        <v>-13.84359356314478</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.21271177599841</v>
       </c>
       <c r="E6">
-        <v>-28.00159467943687</v>
+        <v>-24.36113178230064</v>
       </c>
       <c r="F6">
-        <v>-3.057230869737559</v>
+        <v>-1.765332262618729</v>
       </c>
       <c r="G6">
-        <v>-16.31304866052658</v>
+        <v>-13.78910032829561</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.54204453350397</v>
       </c>
       <c r="E7">
-        <v>-28.42416923146263</v>
+        <v>-25.26823041077709</v>
       </c>
       <c r="F7">
-        <v>-2.888579408364594</v>
+        <v>-1.76540681568498</v>
       </c>
       <c r="G7">
-        <v>-15.96970370628491</v>
+        <v>-14.26184954184907</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.8179749371148</v>
       </c>
       <c r="E8">
-        <v>-28.37513944338158</v>
+        <v>-25.60225518205686</v>
       </c>
       <c r="F8">
-        <v>-2.951859222631851</v>
+        <v>-1.766822495576365</v>
       </c>
       <c r="G8">
-        <v>-15.83746230944595</v>
+        <v>-13.5095280680497</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.0526204587308</v>
       </c>
       <c r="E9">
-        <v>-29.22387962732119</v>
+        <v>-26.00886686320558</v>
       </c>
       <c r="F9">
-        <v>-2.715813446101923</v>
+        <v>-1.503668395789824</v>
       </c>
       <c r="G9">
-        <v>-16.06275486502998</v>
+        <v>-13.39803054955981</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.26669128259598</v>
       </c>
       <c r="E10">
-        <v>-29.9314038778056</v>
+        <v>-27.08179368136891</v>
       </c>
       <c r="F10">
-        <v>-2.966262046664326</v>
+        <v>-1.721783331518753</v>
       </c>
       <c r="G10">
-        <v>-15.68056727997604</v>
+        <v>-13.28635260633804</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.469357470027211</v>
       </c>
       <c r="E11">
-        <v>-30.41650759892927</v>
+        <v>-27.16102386260711</v>
       </c>
       <c r="F11">
-        <v>-2.796802927073631</v>
+        <v>-1.47824662856531</v>
       </c>
       <c r="G11">
-        <v>-15.17879120313425</v>
+        <v>-12.73193223433075</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.661253863330218</v>
       </c>
       <c r="E12">
-        <v>-30.81896214093895</v>
+        <v>-27.73335957854054</v>
       </c>
       <c r="F12">
-        <v>-2.717972999921022</v>
+        <v>-1.491665352123259</v>
       </c>
       <c r="G12">
-        <v>-15.01881405576728</v>
+        <v>-12.73041931501931</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.835364980729345</v>
       </c>
       <c r="E13">
-        <v>-31.24414509399313</v>
+        <v>-28.87377877331419</v>
       </c>
       <c r="F13">
-        <v>-2.701702207395234</v>
+        <v>-1.717680427772687</v>
       </c>
       <c r="G13">
-        <v>-15.0707316861869</v>
+        <v>-12.70602721548596</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.001902747598291</v>
       </c>
       <c r="E14">
-        <v>-32.07633144119769</v>
+        <v>-29.02329087115143</v>
       </c>
       <c r="F14">
-        <v>-2.489342768380955</v>
+        <v>-1.357415988988557</v>
       </c>
       <c r="G14">
-        <v>-14.54035415115857</v>
+        <v>-11.98065027183071</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.159021752811729</v>
       </c>
       <c r="E15">
-        <v>-32.90750114598753</v>
+        <v>-30.3255464057742</v>
       </c>
       <c r="F15">
-        <v>-2.392500820421874</v>
+        <v>-1.294424446577474</v>
       </c>
       <c r="G15">
-        <v>-14.18928403890102</v>
+        <v>-11.92257668198081</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.305885937537655</v>
       </c>
       <c r="E16">
-        <v>-33.18842276681636</v>
+        <v>-30.77643071305891</v>
       </c>
       <c r="F16">
-        <v>-2.159416457356954</v>
+        <v>-1.113407116615518</v>
       </c>
       <c r="G16">
-        <v>-14.10589139676678</v>
+        <v>-11.34945172767664</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.447567903184473</v>
       </c>
       <c r="E17">
-        <v>-34.0611615987596</v>
+        <v>-31.63698342144752</v>
       </c>
       <c r="F17">
-        <v>-2.246023926054448</v>
+        <v>-0.9980610976127005</v>
       </c>
       <c r="G17">
-        <v>-13.5293764438304</v>
+        <v>-11.77560501276487</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.600740337936593</v>
       </c>
       <c r="E18">
-        <v>-34.86010215403686</v>
+        <v>-32.34663605471553</v>
       </c>
       <c r="F18">
-        <v>-1.957117540449676</v>
+        <v>-0.4899778092686097</v>
       </c>
       <c r="G18">
-        <v>-13.27252776816604</v>
+        <v>-10.85594208304641</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.777156971559611</v>
       </c>
       <c r="E19">
-        <v>-35.59890910296625</v>
+        <v>-32.97815892592921</v>
       </c>
       <c r="F19">
-        <v>-1.897004574763321</v>
+        <v>-0.5606739968931307</v>
       </c>
       <c r="G19">
-        <v>-13.05486933059558</v>
+        <v>-10.44076325642087</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.985168181177731</v>
       </c>
       <c r="E20">
-        <v>-36.10289882493891</v>
+        <v>-33.82410730564308</v>
       </c>
       <c r="F20">
-        <v>-1.806162491902716</v>
+        <v>-0.4771505400362594</v>
       </c>
       <c r="G20">
-        <v>-12.93059807214242</v>
+        <v>-10.33843760434754</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.239898613185761</v>
       </c>
       <c r="E21">
-        <v>-36.86577461321907</v>
+        <v>-34.14376096465951</v>
       </c>
       <c r="F21">
-        <v>-1.475278588161079</v>
+        <v>-0.1653016908435519</v>
       </c>
       <c r="G21">
-        <v>-12.82259483446923</v>
+        <v>-10.01608316409762</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.554720036378772</v>
       </c>
       <c r="E22">
-        <v>-37.00710828699847</v>
+        <v>-34.64098061799071</v>
       </c>
       <c r="F22">
-        <v>-1.243926341335413</v>
+        <v>-0.3194666630763595</v>
       </c>
       <c r="G22">
-        <v>-12.35772471929923</v>
+        <v>-10.24973815771385</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.06202146418225229</v>
       </c>
       <c r="E23">
-        <v>-37.26077302277513</v>
+        <v>-35.40423226961351</v>
       </c>
       <c r="F23">
-        <v>-1.343197062519503</v>
+        <v>-0.3365591960657245</v>
       </c>
       <c r="G23">
-        <v>-12.20713131326333</v>
+        <v>-9.473799252037308</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.6099866958397991</v>
       </c>
       <c r="E24">
-        <v>-37.65998064892131</v>
+        <v>-36.13776581056097</v>
       </c>
       <c r="F24">
-        <v>-1.361600072740097</v>
+        <v>-0.06913651905255729</v>
       </c>
       <c r="G24">
-        <v>-12.40678038310016</v>
+        <v>-9.360346856406483</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.082766028140321</v>
       </c>
       <c r="E25">
-        <v>-38.30501875081088</v>
+        <v>-36.22530800584025</v>
       </c>
       <c r="F25">
-        <v>-1.021657143081445</v>
+        <v>0.04837650907598338</v>
       </c>
       <c r="G25">
-        <v>-12.33093909534099</v>
+        <v>-9.322331861979032</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.480558209675284</v>
       </c>
       <c r="E26">
-        <v>-38.46541503592556</v>
+        <v>-35.84822197522154</v>
       </c>
       <c r="F26">
-        <v>-0.8397037579543246</v>
+        <v>-0.01133138495040219</v>
       </c>
       <c r="G26">
-        <v>-12.2239886111493</v>
+        <v>-9.021333751002958</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.806360573660569</v>
       </c>
       <c r="E27">
-        <v>-38.61186814957062</v>
+        <v>-36.30617749466923</v>
       </c>
       <c r="F27">
-        <v>-0.8565867139907813</v>
+        <v>0.03589549741800323</v>
       </c>
       <c r="G27">
-        <v>-12.10800364818093</v>
+        <v>-9.694331243135858</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.065002386020511</v>
       </c>
       <c r="E28">
-        <v>-38.5787944396556</v>
+        <v>-36.67470923788745</v>
       </c>
       <c r="F28">
-        <v>-1.200031152661068</v>
+        <v>-0.006795245052672097</v>
       </c>
       <c r="G28">
-        <v>-12.23234111754488</v>
+        <v>-9.685214000720705</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.254415538880692</v>
       </c>
       <c r="E29">
-        <v>-38.59158285025326</v>
+        <v>-35.55164315551119</v>
       </c>
       <c r="F29">
-        <v>-0.9498633686482141</v>
+        <v>0.1423655596998237</v>
       </c>
       <c r="G29">
-        <v>-12.31920983249535</v>
+        <v>-9.304554232433146</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.374947531555976</v>
       </c>
       <c r="E30">
-        <v>-38.36251225681226</v>
+        <v>-36.27932590804075</v>
       </c>
       <c r="F30">
-        <v>-1.04839021590459</v>
+        <v>0.2304458656394951</v>
       </c>
       <c r="G30">
-        <v>-12.77676364202356</v>
+        <v>-9.587413864399556</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.426478781668642</v>
       </c>
       <c r="E31">
-        <v>-38.14937057069324</v>
+        <v>-36.05876658149716</v>
       </c>
       <c r="F31">
-        <v>-0.9138956560186595</v>
+        <v>0.004366177332648442</v>
       </c>
       <c r="G31">
-        <v>-12.38035891915123</v>
+        <v>-9.882995922873384</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.406581058879856</v>
       </c>
       <c r="E32">
-        <v>-37.51266712521479</v>
+        <v>-34.95446875964569</v>
       </c>
       <c r="F32">
-        <v>-0.9033256879589379</v>
+        <v>-0.08883592425853233</v>
       </c>
       <c r="G32">
-        <v>-12.52711871345266</v>
+        <v>-9.836002728943429</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>2.31193078113769</v>
       </c>
       <c r="E33">
-        <v>-37.74767001960583</v>
+        <v>-35.4121435137049</v>
       </c>
       <c r="F33">
-        <v>-1.112456979204507</v>
+        <v>-0.02567622326468123</v>
       </c>
       <c r="G33">
-        <v>-12.80630695041602</v>
+        <v>-10.17747888022817</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.142210358319005</v>
       </c>
       <c r="E34">
-        <v>-37.58752732903559</v>
+        <v>-33.94923809942303</v>
       </c>
       <c r="F34">
-        <v>-1.068383691538559</v>
+        <v>-0.1164669473463126</v>
       </c>
       <c r="G34">
-        <v>-12.60037115460012</v>
+        <v>-10.03644301916414</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.894791333752301</v>
       </c>
       <c r="E35">
-        <v>-36.71296578630425</v>
+        <v>-34.29631393279291</v>
       </c>
       <c r="F35">
-        <v>-0.8925975017252814</v>
+        <v>0.1487630411516443</v>
       </c>
       <c r="G35">
-        <v>-13.09597306401117</v>
+        <v>-9.982673138515299</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.567990084329566</v>
       </c>
       <c r="E36">
-        <v>-36.38541899709245</v>
+        <v>-34.21266169668622</v>
       </c>
       <c r="F36">
-        <v>-1.104267739060431</v>
+        <v>0.1346451755057323</v>
       </c>
       <c r="G36">
-        <v>-12.92330162977386</v>
+        <v>-9.867942872306317</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.162090177466106</v>
       </c>
       <c r="E37">
-        <v>-36.21225241527614</v>
+        <v>-33.51935006187488</v>
       </c>
       <c r="F37">
-        <v>-1.059751274833985</v>
+        <v>0.1450792913113949</v>
       </c>
       <c r="G37">
-        <v>-13.02819957573121</v>
+        <v>-10.61366311830039</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.6823339855359467</v>
       </c>
       <c r="E38">
-        <v>-35.68606411371788</v>
+        <v>-32.63195708804281</v>
       </c>
       <c r="F38">
-        <v>-1.116321313138566</v>
+        <v>-0.1896109606461062</v>
       </c>
       <c r="G38">
-        <v>-13.27024680228948</v>
+        <v>-10.45683595501403</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.1277612615341931</v>
       </c>
       <c r="E39">
-        <v>-35.08433860147467</v>
+        <v>-32.03437739375362</v>
       </c>
       <c r="F39">
-        <v>-1.054805921439272</v>
+        <v>0.08316048468693742</v>
       </c>
       <c r="G39">
-        <v>-13.13350471878989</v>
+        <v>-10.99700111792922</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.4958990034751388</v>
       </c>
       <c r="E40">
-        <v>-34.42537997048552</v>
+        <v>-31.4675347167915</v>
       </c>
       <c r="F40">
-        <v>-1.016525407021101</v>
+        <v>0.07835595375070029</v>
       </c>
       <c r="G40">
-        <v>-13.32347375346989</v>
+        <v>-10.80249332531488</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.178590673562375</v>
       </c>
       <c r="E41">
-        <v>-34.37650415052074</v>
+        <v>-31.30125820817786</v>
       </c>
       <c r="F41">
-        <v>-0.9346006992516331</v>
+        <v>0.3382081810696828</v>
       </c>
       <c r="G41">
-        <v>-13.01002468072061</v>
+        <v>-10.09511581775665</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.906598397018865</v>
       </c>
       <c r="E42">
-        <v>-33.37049232853175</v>
+        <v>-30.57016098624653</v>
       </c>
       <c r="F42">
-        <v>-0.9800010314968657</v>
+        <v>0.6356566913321237</v>
       </c>
       <c r="G42">
-        <v>-13.50768409418432</v>
+        <v>-10.01805293869349</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.673662300246348</v>
       </c>
       <c r="E43">
-        <v>-33.58908856159301</v>
+        <v>-29.58981655493301</v>
       </c>
       <c r="F43">
-        <v>-0.9165712827297019</v>
+        <v>0.468593210270325</v>
       </c>
       <c r="G43">
-        <v>-12.91301576478335</v>
+        <v>-10.52613229424206</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.468245286089287</v>
       </c>
       <c r="E44">
-        <v>-32.73213146156649</v>
+        <v>-29.63401898972188</v>
       </c>
       <c r="F44">
-        <v>-0.8615386943247167</v>
+        <v>0.5371538667304289</v>
       </c>
       <c r="G44">
-        <v>-13.17884926104128</v>
+        <v>-10.52814179538439</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.274739980296403</v>
       </c>
       <c r="E45">
-        <v>-32.66308128989753</v>
+        <v>-28.74128468079777</v>
       </c>
       <c r="F45">
-        <v>-0.6811086768513452</v>
+        <v>0.5229125743414997</v>
       </c>
       <c r="G45">
-        <v>-13.52915629255203</v>
+        <v>-10.28966995800853</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.082189401502132</v>
       </c>
       <c r="E46">
-        <v>-31.41598256868819</v>
+        <v>-28.5757644273434</v>
       </c>
       <c r="F46">
-        <v>-0.7485369550718222</v>
+        <v>0.6210285513660873</v>
       </c>
       <c r="G46">
-        <v>-13.06109646675495</v>
+        <v>-10.53433582608837</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.884445811178625</v>
       </c>
       <c r="E47">
-        <v>-31.15426847036289</v>
+        <v>-27.95475214430153</v>
       </c>
       <c r="F47">
-        <v>-0.6633310840198651</v>
+        <v>0.6696876809739329</v>
       </c>
       <c r="G47">
-        <v>-13.35536423864968</v>
+        <v>-10.58450714373603</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.673704998782649</v>
       </c>
       <c r="E48">
-        <v>-30.25285081252906</v>
+        <v>-27.77246748007078</v>
       </c>
       <c r="F48">
-        <v>-0.5399606699861291</v>
+        <v>0.657875161810012</v>
       </c>
       <c r="G48">
-        <v>-13.31690563111997</v>
+        <v>-11.18840030828218</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.434473988929068</v>
       </c>
       <c r="E49">
-        <v>-30.24515014247902</v>
+        <v>-26.38856582332672</v>
       </c>
       <c r="F49">
-        <v>-0.506594031001365</v>
+        <v>0.6825091516344637</v>
       </c>
       <c r="G49">
-        <v>-13.22641517934953</v>
+        <v>-10.46342725118272</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.163858962249567</v>
       </c>
       <c r="E50">
-        <v>-29.67174570667979</v>
+        <v>-25.68457378256829</v>
       </c>
       <c r="F50">
-        <v>-0.5737506047137237</v>
+        <v>0.6154776613999278</v>
       </c>
       <c r="G50">
-        <v>-13.04115705097192</v>
+        <v>-10.42343586106833</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.858159409111041</v>
       </c>
       <c r="E51">
-        <v>-29.14317316355649</v>
+        <v>-25.72427944266754</v>
       </c>
       <c r="F51">
-        <v>-0.6959165725437892</v>
+        <v>0.9537431470679114</v>
       </c>
       <c r="G51">
-        <v>-13.04282225537817</v>
+        <v>-10.61750666167148</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.512559303689631</v>
       </c>
       <c r="E52">
-        <v>-29.00960582270025</v>
+        <v>-25.2895504664052</v>
       </c>
       <c r="F52">
-        <v>-0.4048995067966837</v>
+        <v>0.6983218569865035</v>
       </c>
       <c r="G52">
-        <v>-13.04067702186872</v>
+        <v>-10.43785990798293</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.1144531747616</v>
       </c>
       <c r="E53">
-        <v>-28.15791307370765</v>
+        <v>-24.42085329751379</v>
       </c>
       <c r="F53">
-        <v>-0.507412457995331</v>
+        <v>0.9602044128097476</v>
       </c>
       <c r="G53">
-        <v>-13.20299638020473</v>
+        <v>-10.76207156428038</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.66462475288044</v>
       </c>
       <c r="E54">
-        <v>-27.62160589697925</v>
+        <v>-23.89970292328906</v>
       </c>
       <c r="F54">
-        <v>-0.6790112505874569</v>
+        <v>0.9549393095975539</v>
       </c>
       <c r="G54">
-        <v>-13.46867097027678</v>
+        <v>-11.1440687929658</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.16278154829897</v>
       </c>
       <c r="E55">
-        <v>-27.53746232144272</v>
+        <v>-24.19345597521863</v>
       </c>
       <c r="F55">
-        <v>-0.5220331426547422</v>
+        <v>0.7358063103305839</v>
       </c>
       <c r="G55">
-        <v>-13.28104911238413</v>
+        <v>-11.07764269672032</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.6024050117572</v>
       </c>
       <c r="E56">
-        <v>-27.29109975000343</v>
+        <v>-23.0552919605008</v>
       </c>
       <c r="F56">
-        <v>-0.6558774341294751</v>
+        <v>0.6913470034549316</v>
       </c>
       <c r="G56">
-        <v>-13.38204061460513</v>
+        <v>-10.50291212782961</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.97379265988119</v>
       </c>
       <c r="E57">
-        <v>-26.21343614802808</v>
+        <v>-23.497615187674</v>
       </c>
       <c r="F57">
-        <v>-0.6328380515554125</v>
+        <v>0.9906933034371862</v>
       </c>
       <c r="G57">
-        <v>-13.4200986461246</v>
+        <v>-11.28935208395672</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.27444978004196</v>
       </c>
       <c r="E58">
-        <v>-25.89751621583097</v>
+        <v>-22.81663232334855</v>
       </c>
       <c r="F58">
-        <v>-0.7293039207136233</v>
+        <v>0.6622207772050982</v>
       </c>
       <c r="G58">
-        <v>-13.68731263987241</v>
+        <v>-11.91350247665767</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.50436975313925</v>
       </c>
       <c r="E59">
-        <v>-25.81817282274258</v>
+        <v>-22.20835410921625</v>
       </c>
       <c r="F59">
-        <v>-0.6639954346769102</v>
+        <v>0.5739797679892837</v>
       </c>
       <c r="G59">
-        <v>-13.6341949366948</v>
+        <v>-11.13502438255251</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.65409044061516</v>
       </c>
       <c r="E60">
-        <v>-25.81972608932721</v>
+        <v>-21.25962974766129</v>
       </c>
       <c r="F60">
-        <v>-0.8365601036607004</v>
+        <v>0.6591491908755177</v>
       </c>
       <c r="G60">
-        <v>-13.60955620151877</v>
+        <v>-11.55011713499403</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.71849955371595</v>
       </c>
       <c r="E61">
-        <v>-25.55828822791639</v>
+        <v>-21.42324804203243</v>
       </c>
       <c r="F61">
-        <v>-0.6745935672283272</v>
+        <v>0.5837346225246507</v>
       </c>
       <c r="G61">
-        <v>-13.70620095744672</v>
+        <v>-11.34981588768597</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-12.70037292514643</v>
       </c>
       <c r="E62">
-        <v>-25.12249053178823</v>
+        <v>-21.37393748856291</v>
       </c>
       <c r="F62">
-        <v>-0.8886644132967894</v>
+        <v>0.4434787673522496</v>
       </c>
       <c r="G62">
-        <v>-13.66895069903884</v>
+        <v>-11.59938136316392</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-12.6060409100163</v>
       </c>
       <c r="E63">
-        <v>-24.65869780934466</v>
+        <v>-21.47156685969427</v>
       </c>
       <c r="F63">
-        <v>-0.99960848792113</v>
+        <v>0.2906507801075604</v>
       </c>
       <c r="G63">
-        <v>-13.88927909158672</v>
+        <v>-11.56458752954618</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-12.43235390046711</v>
       </c>
       <c r="E64">
-        <v>-24.66414103510187</v>
+        <v>-20.80973944042126</v>
       </c>
       <c r="F64">
-        <v>-0.9637401793799114</v>
+        <v>0.5431595304007253</v>
       </c>
       <c r="G64">
-        <v>-14.03657022844721</v>
+        <v>-11.7447374861567</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-12.18380229985507</v>
       </c>
       <c r="E65">
-        <v>-24.5596600827969</v>
+        <v>-21.30914408246116</v>
       </c>
       <c r="F65">
-        <v>-1.170661386394811</v>
+        <v>0.3355043898669452</v>
       </c>
       <c r="G65">
-        <v>-13.77005641508095</v>
+        <v>-11.86665494673144</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.87288443495405</v>
       </c>
       <c r="E66">
-        <v>-24.08694173808421</v>
+        <v>-20.45962952946624</v>
       </c>
       <c r="F66">
-        <v>-1.139024378547092</v>
+        <v>0.07986606752600378</v>
       </c>
       <c r="G66">
-        <v>-14.03336230981965</v>
+        <v>-11.61969156004735</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.50940843058379</v>
       </c>
       <c r="E67">
-        <v>-24.37041968249037</v>
+        <v>-21.0601459391494</v>
       </c>
       <c r="F67">
-        <v>-1.369101767939849</v>
+        <v>-0.1974779658704931</v>
       </c>
       <c r="G67">
-        <v>-13.93434720328559</v>
+        <v>-11.59259474480842</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.09726785610369</v>
       </c>
       <c r="E68">
-        <v>-24.29570891831182</v>
+        <v>-20.57722494249743</v>
       </c>
       <c r="F68">
-        <v>-1.389881364239075</v>
+        <v>-0.0714725151284519</v>
       </c>
       <c r="G68">
-        <v>-13.86891096015636</v>
+        <v>-11.90767922705409</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.64268691065161</v>
       </c>
       <c r="E69">
-        <v>-24.30486096428132</v>
+        <v>-20.4026884972938</v>
       </c>
       <c r="F69">
-        <v>-1.619059974999795</v>
+        <v>-0.3372359722338117</v>
       </c>
       <c r="G69">
-        <v>-13.65770974166024</v>
+        <v>-11.84417634251979</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.16294840715031</v>
       </c>
       <c r="E70">
-        <v>-24.1962183443633</v>
+        <v>-19.89493334918376</v>
       </c>
       <c r="F70">
-        <v>-1.653970690823377</v>
+        <v>-0.4164883667618488</v>
       </c>
       <c r="G70">
-        <v>-13.81408667075326</v>
+        <v>-11.05785225548656</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.664165059714939</v>
       </c>
       <c r="E71">
-        <v>-24.13132984030739</v>
+        <v>-19.48569062463658</v>
       </c>
       <c r="F71">
-        <v>-1.772144756139352</v>
+        <v>-0.4635156125861795</v>
       </c>
       <c r="G71">
-        <v>-13.42509094879781</v>
+        <v>-11.25762381550834</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.147921340323251</v>
       </c>
       <c r="E72">
-        <v>-24.26648214706632</v>
+        <v>-19.8872213579487</v>
       </c>
       <c r="F72">
-        <v>-1.872696961695572</v>
+        <v>-0.5793893016245799</v>
       </c>
       <c r="G72">
-        <v>-13.54313838163715</v>
+        <v>-11.19927213983315</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.613819848367804</v>
       </c>
       <c r="E73">
-        <v>-23.75389058871609</v>
+        <v>-20.12746143252962</v>
       </c>
       <c r="F73">
-        <v>-1.814439538991489</v>
+        <v>-0.4769484183899763</v>
       </c>
       <c r="G73">
-        <v>-13.54668397590971</v>
+        <v>-11.54274455007807</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.06816320410571</v>
       </c>
       <c r="E74">
-        <v>-24.4837356875843</v>
+        <v>-20.30991365029866</v>
       </c>
       <c r="F74">
-        <v>-1.975905741512571</v>
+        <v>-0.9580062202177332</v>
       </c>
       <c r="G74">
-        <v>-13.21089203131589</v>
+        <v>-11.09704580412599</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.505620921382466</v>
       </c>
       <c r="E75">
-        <v>-24.38943474484858</v>
+        <v>-20.63514865352954</v>
       </c>
       <c r="F75">
-        <v>-1.979149628261934</v>
+        <v>-0.7056159264631686</v>
       </c>
       <c r="G75">
-        <v>-13.10550743516427</v>
+        <v>-11.24968181675963</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.918617510160194</v>
       </c>
       <c r="E76">
-        <v>-24.50360663152996</v>
+        <v>-20.33383757848118</v>
       </c>
       <c r="F76">
-        <v>-2.123630157188613</v>
+        <v>-0.9950176757748151</v>
       </c>
       <c r="G76">
-        <v>-13.35455315499256</v>
+        <v>-10.61794034313713</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.304824916479258</v>
       </c>
       <c r="E77">
-        <v>-24.28732671292362</v>
+        <v>-21.04767452173228</v>
       </c>
       <c r="F77">
-        <v>-2.181892550097113</v>
+        <v>-0.9792115973619977</v>
       </c>
       <c r="G77">
-        <v>-13.16655389490843</v>
+        <v>-10.86148393627915</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.664590778038517</v>
       </c>
       <c r="E78">
-        <v>-25.05810921682118</v>
+        <v>-21.35352765621034</v>
       </c>
       <c r="F78">
-        <v>-2.375853949095215</v>
+        <v>-0.984263810151672</v>
       </c>
       <c r="G78">
-        <v>-12.77797861223648</v>
+        <v>-10.56797758985845</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.99484058675518</v>
       </c>
       <c r="E79">
-        <v>-25.4676145928608</v>
+        <v>-21.76729432629118</v>
       </c>
       <c r="F79">
-        <v>-2.396091793113009</v>
+        <v>-1.390196143852139</v>
       </c>
       <c r="G79">
-        <v>-12.33007504295524</v>
+        <v>-10.29876071605937</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.287507021873806</v>
       </c>
       <c r="E80">
-        <v>-25.72983588027495</v>
+        <v>-21.67870378927912</v>
       </c>
       <c r="F80">
-        <v>-2.405182296991331</v>
+        <v>-1.244252718092116</v>
       </c>
       <c r="G80">
-        <v>-12.69889298984883</v>
+        <v>-9.982643343605446</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.544788172886501</v>
       </c>
       <c r="E81">
-        <v>-26.05343610438907</v>
+        <v>-21.38582926130705</v>
       </c>
       <c r="F81">
-        <v>-2.537837052875644</v>
+        <v>-1.096519190374644</v>
       </c>
       <c r="G81">
-        <v>-12.23407584340746</v>
+        <v>-10.02661732000359</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.767725241863002</v>
       </c>
       <c r="E82">
-        <v>-26.32264029872305</v>
+        <v>-22.3142434169376</v>
       </c>
       <c r="F82">
-        <v>-2.476160129532804</v>
+        <v>-1.363901277385074</v>
       </c>
       <c r="G82">
-        <v>-12.14879619031583</v>
+        <v>-9.194862616534936</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.959531122604021</v>
       </c>
       <c r="E83">
-        <v>-27.46627923851615</v>
+        <v>-23.69319092311727</v>
       </c>
       <c r="F83">
-        <v>-2.521919144863449</v>
+        <v>-1.418527965762687</v>
       </c>
       <c r="G83">
-        <v>-12.09001745426607</v>
+        <v>-9.313201377381723</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.116294799224507</v>
       </c>
       <c r="E84">
-        <v>-27.61335501733727</v>
+        <v>-24.29613912334255</v>
       </c>
       <c r="F84">
-        <v>-2.718634037108456</v>
+        <v>-1.244523594232832</v>
       </c>
       <c r="G84">
-        <v>-11.8232536947116</v>
+        <v>-9.342503015949813</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.2474765629807819</v>
       </c>
       <c r="E85">
-        <v>-28.14449973369693</v>
+        <v>-24.15423486183819</v>
       </c>
       <c r="F85">
-        <v>-2.65439000318434</v>
+        <v>-1.404433294404054</v>
       </c>
       <c r="G85">
-        <v>-11.88067179654472</v>
+        <v>-9.413398348673304</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.6399025013858496</v>
       </c>
       <c r="E86">
-        <v>-28.96927070471393</v>
+        <v>-25.65929584065747</v>
       </c>
       <c r="F86">
-        <v>-2.806459205888065</v>
+        <v>-1.382867577439572</v>
       </c>
       <c r="G86">
-        <v>-11.69711859911983</v>
+        <v>-9.416212312381685</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.538402808368004</v>
       </c>
       <c r="E87">
-        <v>-30.03645088936153</v>
+        <v>-26.84824216289732</v>
       </c>
       <c r="F87">
-        <v>-2.935685349092191</v>
+        <v>-1.659419691598992</v>
       </c>
       <c r="G87">
-        <v>-11.6310930788846</v>
+        <v>-9.004794265488758</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.44312258206029</v>
       </c>
       <c r="E88">
-        <v>-30.31048017275068</v>
+        <v>-27.59594303477778</v>
       </c>
       <c r="F88">
-        <v>-3.010481126993166</v>
+        <v>-1.748802191095864</v>
       </c>
       <c r="G88">
-        <v>-11.68572370137366</v>
+        <v>-9.13333612768758</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>3.339549228922502</v>
       </c>
       <c r="E89">
-        <v>-31.83480754423559</v>
+        <v>-29.28318905139965</v>
       </c>
       <c r="F89">
-        <v>-3.125290363918969</v>
+        <v>-1.819456960350246</v>
       </c>
       <c r="G89">
-        <v>-11.93591486995854</v>
+        <v>-9.161955793874579</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>4.209491661977856</v>
       </c>
       <c r="E90">
-        <v>-32.28517560548343</v>
+        <v>-29.10391129390998</v>
       </c>
       <c r="F90">
-        <v>-3.035584801135005</v>
+        <v>-1.92823319748146</v>
       </c>
       <c r="G90">
-        <v>-11.78754615052502</v>
+        <v>-8.985738765364713</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>5.037947786568017</v>
       </c>
       <c r="E91">
-        <v>-33.87928223295254</v>
+        <v>-31.07458770596093</v>
       </c>
       <c r="F91">
-        <v>-3.316456022932623</v>
+        <v>-2.001185857911207</v>
       </c>
       <c r="G91">
-        <v>-11.86150373787234</v>
+        <v>-8.667969430686691</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>5.806893389162719</v>
       </c>
       <c r="E92">
-        <v>-34.88096256955319</v>
+        <v>-32.76048650156552</v>
       </c>
       <c r="F92">
-        <v>-3.442642886135877</v>
+        <v>-2.19778726382203</v>
       </c>
       <c r="G92">
-        <v>-12.10856313037707</v>
+        <v>-9.732452175020565</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>6.49590850902157</v>
       </c>
       <c r="E93">
-        <v>-36.0622738846161</v>
+        <v>-34.01599007053309</v>
       </c>
       <c r="F93">
-        <v>-3.395828530734065</v>
+        <v>-2.37983839630268</v>
       </c>
       <c r="G93">
-        <v>-12.29881025088237</v>
+        <v>-9.260269064754317</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>7.080773602889387</v>
       </c>
       <c r="E94">
-        <v>-37.04375722714254</v>
+        <v>-34.74084705528186</v>
       </c>
       <c r="F94">
-        <v>-3.435084861952734</v>
+        <v>-2.557253984797264</v>
       </c>
       <c r="G94">
-        <v>-12.20320500625375</v>
+        <v>-10.10098541499777</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>7.551119665382227</v>
       </c>
       <c r="E95">
-        <v>-38.83479813225722</v>
+        <v>-36.39958406378844</v>
       </c>
       <c r="F95">
-        <v>-3.717208575263384</v>
+        <v>-2.448845542792893</v>
       </c>
       <c r="G95">
-        <v>-11.95512596572293</v>
+        <v>-9.934402074007187</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>7.889348550372182</v>
       </c>
       <c r="E96">
-        <v>-39.88076920888989</v>
+        <v>-38.5074709740348</v>
       </c>
       <c r="F96">
-        <v>-3.809447285565109</v>
+        <v>-2.817250348044334</v>
       </c>
       <c r="G96">
-        <v>-12.72100412350562</v>
+        <v>-9.683072077756796</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>8.095000080225617</v>
       </c>
       <c r="E97">
-        <v>-42.15999319745346</v>
+        <v>-40.42113842680318</v>
       </c>
       <c r="F97">
-        <v>-4.12257264892553</v>
+        <v>-2.78020575779114</v>
       </c>
       <c r="G97">
-        <v>-13.03677388867792</v>
+        <v>-9.685452359999532</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>8.145308999767511</v>
       </c>
       <c r="E98">
-        <v>-43.41631189174242</v>
+        <v>-41.49513396483231</v>
       </c>
       <c r="F98">
-        <v>-4.077435737514389</v>
+        <v>-2.904606660873958</v>
       </c>
       <c r="G98">
-        <v>-13.54037573138462</v>
+        <v>-10.48799812017519</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>8.067224318329794</v>
       </c>
       <c r="E99">
-        <v>-45.24574746373113</v>
+        <v>-43.4833106646859</v>
       </c>
       <c r="F99">
-        <v>-4.253946748805116</v>
+        <v>-3.163530288334403</v>
       </c>
       <c r="G99">
-        <v>-13.36793769060784</v>
+        <v>-10.66461903524085</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>7.832556140053766</v>
       </c>
       <c r="E100">
-        <v>-46.93654606821201</v>
+        <v>-45.82292864685276</v>
       </c>
       <c r="F100">
-        <v>-4.324146744355359</v>
+        <v>-3.399185075450209</v>
       </c>
       <c r="G100">
-        <v>-13.70295993336377</v>
+        <v>-11.68766699160521</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>7.506644346853863</v>
       </c>
       <c r="E101">
-        <v>-48.94531713573398</v>
+        <v>-47.79307975591881</v>
       </c>
       <c r="F101">
-        <v>-4.650651898005798</v>
+        <v>-3.286114581702882</v>
       </c>
       <c r="G101">
-        <v>-14.18244114127135</v>
+        <v>-10.94653185118303</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>6.997824436029673</v>
       </c>
       <c r="E102">
-        <v>-50.87172431800444</v>
+        <v>-49.18323070679346</v>
       </c>
       <c r="F102">
-        <v>-4.733267464189201</v>
+        <v>-3.777462363408215</v>
       </c>
       <c r="G102">
-        <v>-14.23417834695907</v>
+        <v>-11.22862343658432</v>
       </c>
     </row>
   </sheetData>
